--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_3/epoch_70/per_file_predictions_epoch_70.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_3/epoch_70/per_file_predictions_epoch_70.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9863,0.0019,0.0034,0.0009</t>
-  </si>
-  <si>
-    <t>0.9710,0.0022,0.0036,0.0134</t>
-  </si>
-  <si>
-    <t>0.9839,0.0003,0.0023,0.0035</t>
-  </si>
-  <si>
-    <t>0.9891,0.0003,0.0014,0.0016</t>
-  </si>
-  <si>
-    <t>0.9732,0.0006,0.0005,0.0221</t>
-  </si>
-  <si>
-    <t>0.9484,0.0026,0.0015,0.0352</t>
-  </si>
-  <si>
-    <t>0.9231,0.0017,0.0034,0.0615</t>
-  </si>
-  <si>
-    <t>0.9501,0.0003,0.0002,0.0954</t>
-  </si>
-  <si>
-    <t>0.9887,0.0004,0.0002,0.0095</t>
-  </si>
-  <si>
-    <t>0.9475,0.0072,0.0048,0.0113</t>
-  </si>
-  <si>
-    <t>0.9767,0.0038,0.0020,0.0043</t>
-  </si>
-  <si>
-    <t>0.9775,0.0007,0.0013,0.0119</t>
-  </si>
-  <si>
-    <t>0.9491,0.0026,0.0511,0.0011</t>
-  </si>
-  <si>
-    <t>0.9486,0.0012,0.0523,0.0014</t>
-  </si>
-  <si>
-    <t>0.7306,0.0155,0.3862,0.0021</t>
-  </si>
-  <si>
-    <t>0.9436,0.0017,0.0798,0.0005</t>
-  </si>
-  <si>
-    <t>0.9330,0.0022,0.0891,0.0021</t>
-  </si>
-  <si>
-    <t>0.9836,0.0055,0.0032,0.0003</t>
-  </si>
-  <si>
-    <t>0.9769,0.0045,0.0068,0.0006</t>
-  </si>
-  <si>
-    <t>0.9727,0.0049,0.0062,0.0015</t>
-  </si>
-  <si>
-    <t>0.8463,0.0828,0.0280,0.0008</t>
-  </si>
-  <si>
-    <t>0.9705,0.0138,0.0042,0.0004</t>
-  </si>
-  <si>
-    <t>0.9617,0.0004,0.0598,0.0002</t>
-  </si>
-  <si>
-    <t>0.9660,0.0009,0.0436,0.0005</t>
-  </si>
-  <si>
-    <t>0.1365,0.0018,0.9546,0.0005</t>
-  </si>
-  <si>
-    <t>0.9218,0.0016,0.1182,0.0006</t>
-  </si>
-  <si>
-    <t>0.2104,0.0111,0.8889,0.0016</t>
-  </si>
-  <si>
-    <t>0.9482,0.0010,0.1089,0.0001</t>
-  </si>
-  <si>
-    <t>0.1812,0.0064,0.9114,0.0018</t>
-  </si>
-  <si>
-    <t>0.9769,0.0070,0.0050,0.0004</t>
-  </si>
-  <si>
-    <t>0.9757,0.0035,0.0108,0.0009</t>
-  </si>
-  <si>
-    <t>0.0631,0.0166,0.9528,0.0015</t>
-  </si>
-  <si>
-    <t>0.9262,0.0226,0.0238,0.0002</t>
-  </si>
-  <si>
-    <t>0.9355,0.0143,0.0085,0.0045</t>
-  </si>
-  <si>
-    <t>0.9609,0.0026,0.0145,0.0027</t>
-  </si>
-  <si>
-    <t>0.7407,0.1099,0.0600,0.0212</t>
-  </si>
-  <si>
-    <t>0.8367,0.0441,0.0902,0.0260</t>
-  </si>
-  <si>
-    <t>0.5933,0.0983,0.3380,0.0027</t>
-  </si>
-  <si>
-    <t>0.7558,0.0004,0.3924,0.0005</t>
-  </si>
-  <si>
-    <t>0.5582,0.0049,0.6849,0.0005</t>
-  </si>
-  <si>
-    <t>0.0434,0.0005,0.9707,0.0010</t>
-  </si>
-  <si>
-    <t>0.9353,0.0032,0.1138,0.0004</t>
-  </si>
-  <si>
-    <t>0.0998,0.8377,0.1019,0.0011</t>
-  </si>
-  <si>
-    <t>0.6173,0.0047,0.6564,0.0006</t>
-  </si>
-  <si>
-    <t>0.8991,0.0156,0.0669,0.0088</t>
-  </si>
-  <si>
-    <t>0.9881,0.0035,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.9907,0.0030,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.7960,0.1137,0.0415,0.0006</t>
-  </si>
-  <si>
-    <t>0.0743,0.0115,0.9525,0.0004</t>
-  </si>
-  <si>
-    <t>0.0383,0.0351,0.9795,0.0002</t>
-  </si>
-  <si>
-    <t>0.9568,0.0012,0.0546,0.0006</t>
-  </si>
-  <si>
-    <t>0.8087,0.0008,0.2866,0.0009</t>
-  </si>
-  <si>
-    <t>0.0546,0.0022,0.9778,0.0008</t>
-  </si>
-  <si>
-    <t>0.2532,0.0313,0.8462,0.0020</t>
-  </si>
-  <si>
-    <t>0.9617,0.0013,0.0024,0.0241</t>
-  </si>
-  <si>
-    <t>0.9484,0.0023,0.0030,0.0333</t>
-  </si>
-  <si>
-    <t>0.9599,0.0023,0.0011,0.0272</t>
-  </si>
-  <si>
-    <t>0.3257,0.0939,0.6848,0.0723</t>
-  </si>
-  <si>
-    <t>0.9057,0.0051,0.0106,0.0412</t>
-  </si>
-  <si>
-    <t>0.9320,0.0014,0.0004,0.0544</t>
-  </si>
-  <si>
-    <t>0.9709,0.0024,0.0010,0.0078</t>
-  </si>
-  <si>
-    <t>0.5914,0.0554,0.5165,0.0010</t>
-  </si>
-  <si>
-    <t>0.6586,0.0094,0.6250,0.0004</t>
-  </si>
-  <si>
-    <t>0.4515,0.0052,0.7897,0.0004</t>
-  </si>
-  <si>
-    <t>0.3362,0.3596,0.3151,0.0012</t>
-  </si>
-  <si>
-    <t>0.0732,0.0129,0.9748,0.0001</t>
-  </si>
-  <si>
-    <t>0.9391,0.0367,0.0085,0.0004</t>
-  </si>
-  <si>
-    <t>0.4007,0.7138,0.0151,0.0005</t>
-  </si>
-  <si>
-    <t>0.9760,0.0011,0.0146,0.0013</t>
-  </si>
-  <si>
-    <t>0.9814,0.0014,0.0077,0.0007</t>
-  </si>
-  <si>
-    <t>0.2995,0.0861,0.7079,0.0106</t>
-  </si>
-  <si>
-    <t>0.3377,0.0867,0.7634,0.0018</t>
-  </si>
-  <si>
-    <t>0.7630,0.0210,0.3512,0.0006</t>
-  </si>
-  <si>
-    <t>0.0208,0.9489,0.4525,0.0009</t>
-  </si>
-  <si>
-    <t>0.0302,0.8845,0.6782,0.0030</t>
-  </si>
-  <si>
-    <t>0.8968,0.0005,0.0033,0.0852</t>
-  </si>
-  <si>
-    <t>0.8293,0.0004,0.0037,0.1853</t>
-  </si>
-  <si>
-    <t>0.4747,0.0002,0.0019,0.7334</t>
-  </si>
-  <si>
-    <t>0.5752,0.0007,0.0057,0.5306</t>
-  </si>
-  <si>
-    <t>0.9636,0.0001,0.0002,0.0572</t>
-  </si>
-  <si>
-    <t>0.9940,0.0000,0.0002,0.0025</t>
-  </si>
-  <si>
-    <t>0.1412,0.2650,0.8943,0.0013</t>
-  </si>
-  <si>
-    <t>0.0495,0.0303,0.9742,0.0001</t>
-  </si>
-  <si>
-    <t>0.7414,0.0158,0.3493,0.0021</t>
-  </si>
-  <si>
-    <t>0.0198,0.0459,0.9878,0.0003</t>
-  </si>
-  <si>
-    <t>0.0476,0.7656,0.8213,0.0012</t>
-  </si>
-  <si>
-    <t>0.0843,0.4193,0.9121,0.0039</t>
-  </si>
-  <si>
-    <t>0.9447,0.0033,0.0013,0.0324</t>
-  </si>
-  <si>
-    <t>0.9760,0.0021,0.0035,0.0055</t>
-  </si>
-  <si>
-    <t>0.9508,0.0038,0.0037,0.0197</t>
-  </si>
-  <si>
-    <t>0.9305,0.0011,0.0012,0.0777</t>
-  </si>
-  <si>
-    <t>0.9891,0.0006,0.0004,0.0029</t>
-  </si>
-  <si>
-    <t>0.9580,0.0011,0.0005,0.0368</t>
-  </si>
-  <si>
-    <t>0.9860,0.0004,0.0006,0.0069</t>
-  </si>
-  <si>
-    <t>0.9846,0.0012,0.0016,0.0046</t>
-  </si>
-  <si>
-    <t>0.9716,0.0006,0.0007,0.0203</t>
-  </si>
-  <si>
-    <t>0.9536,0.0020,0.0012,0.0407</t>
-  </si>
-  <si>
-    <t>0.8635,0.0034,0.0087,0.1373</t>
-  </si>
-  <si>
-    <t>0.9384,0.0105,0.0062,0.0121</t>
-  </si>
-  <si>
-    <t>0.9768,0.0008,0.0004,0.0213</t>
-  </si>
-  <si>
-    <t>0.9785,0.0011,0.0006,0.0149</t>
-  </si>
-  <si>
-    <t>0.8933,0.0013,0.0011,0.1493</t>
-  </si>
-  <si>
-    <t>0.9055,0.0035,0.0030,0.0741</t>
-  </si>
-  <si>
-    <t>0.0032,0.0081,0.9978,0.0002</t>
-  </si>
-  <si>
-    <t>0.7072,0.0094,0.5028,0.0014</t>
-  </si>
-  <si>
-    <t>0.9824,0.0009,0.0135,0.0004</t>
-  </si>
-  <si>
-    <t>0.9499,0.0024,0.0709,0.0006</t>
-  </si>
-  <si>
-    <t>0.9374,0.0190,0.0148,0.0028</t>
-  </si>
-  <si>
-    <t>0.7868,0.1148,0.0379,0.0051</t>
-  </si>
-  <si>
-    <t>0.9089,0.0408,0.0074,0.0042</t>
-  </si>
-  <si>
-    <t>0.9773,0.0040,0.0055,0.0011</t>
-  </si>
-  <si>
-    <t>0.9188,0.0368,0.0147,0.0027</t>
-  </si>
-  <si>
-    <t>0.7199,0.1738,0.0524,0.0018</t>
-  </si>
-  <si>
-    <t>0.9547,0.0228,0.0059,0.0006</t>
-  </si>
-  <si>
-    <t>0.9782,0.0004,0.0115,0.0009</t>
-  </si>
-  <si>
-    <t>0.8790,0.0062,0.1541,0.0038</t>
-  </si>
-  <si>
-    <t>0.9752,0.0029,0.0102,0.0007</t>
-  </si>
-  <si>
-    <t>0.9434,0.0051,0.0587,0.0020</t>
-  </si>
-  <si>
-    <t>0.8553,0.0086,0.1277,0.0075</t>
-  </si>
-  <si>
-    <t>0.9715,0.0184,0.0020,0.0002</t>
-  </si>
-  <si>
-    <t>0.9896,0.0021,0.0019,0.0002</t>
-  </si>
-  <si>
-    <t>0.8710,0.0069,0.1317,0.0021</t>
-  </si>
-  <si>
-    <t>0.7107,0.2549,0.0327,0.0008</t>
-  </si>
-  <si>
-    <t>0.9923,0.0009,0.0011,0.0006</t>
-  </si>
-  <si>
-    <t>0.8168,0.0775,0.0603,0.0057</t>
-  </si>
-  <si>
-    <t>0.9251,0.0182,0.0274,0.0046</t>
-  </si>
-  <si>
-    <t>0.9848,0.0014,0.0026,0.0029</t>
-  </si>
-  <si>
-    <t>0.9827,0.0005,0.0007,0.0072</t>
-  </si>
-  <si>
-    <t>0.9592,0.0020,0.0022,0.0182</t>
-  </si>
-  <si>
-    <t>0.9762,0.0010,0.0021,0.0101</t>
-  </si>
-  <si>
-    <t>0.9552,0.0015,0.0019,0.0368</t>
-  </si>
-  <si>
-    <t>0.9862,0.0006,0.0018,0.0035</t>
-  </si>
-  <si>
-    <t>0.9603,0.0014,0.0046,0.0145</t>
-  </si>
-  <si>
-    <t>0.9240,0.0043,0.0060,0.0497</t>
-  </si>
-  <si>
-    <t>0.3481,0.0322,0.8845,0.0012</t>
-  </si>
-  <si>
-    <t>0.8389,0.0083,0.2689,0.0005</t>
-  </si>
-  <si>
-    <t>0.6606,0.0045,0.6326,0.0002</t>
-  </si>
-  <si>
-    <t>0.9643,0.0009,0.0543,0.0001</t>
-  </si>
-  <si>
-    <t>0.9881,0.0002,0.0056,0.0004</t>
-  </si>
-  <si>
-    <t>0.9900,0.0003,0.0060,0.0004</t>
-  </si>
-  <si>
-    <t>0.9395,0.0017,0.1108,0.0007</t>
-  </si>
-  <si>
-    <t>0.9901,0.0009,0.0035,0.0003</t>
-  </si>
-  <si>
-    <t>0.8425,0.0002,0.0015,0.2152</t>
-  </si>
-  <si>
-    <t>0.4519,0.0001,0.0005,0.7999</t>
-  </si>
-  <si>
-    <t>0.7608,0.0003,0.0007,0.4009</t>
-  </si>
-  <si>
-    <t>0.5519,0.0000,0.0007,0.5869</t>
-  </si>
-  <si>
-    <t>0.7928,0.0410,0.1273,0.0025</t>
-  </si>
-  <si>
-    <t>0.9595,0.0018,0.0051,0.0133</t>
-  </si>
-  <si>
-    <t>0.9142,0.0197,0.0082,0.0100</t>
-  </si>
-  <si>
-    <t>0.8828,0.0014,0.0037,0.1229</t>
-  </si>
-  <si>
-    <t>0.9502,0.0056,0.0035,0.0102</t>
-  </si>
-  <si>
-    <t>0.9816,0.0014,0.0020,0.0060</t>
-  </si>
-  <si>
-    <t>0.9812,0.0013,0.0036,0.0031</t>
-  </si>
-  <si>
-    <t>0.9931,0.0003,0.0002,0.0014</t>
-  </si>
-  <si>
-    <t>0.3759,0.1463,0.7701,0.0138</t>
-  </si>
-  <si>
-    <t>0.9437,0.0006,0.0020,0.0440</t>
-  </si>
-  <si>
-    <t>0.9852,0.0008,0.0006,0.0063</t>
-  </si>
-  <si>
-    <t>0.9598,0.0065,0.0150,0.0016</t>
-  </si>
-  <si>
-    <t>0.9652,0.0006,0.0038,0.0140</t>
-  </si>
-  <si>
-    <t>0.9577,0.0057,0.0288,0.0020</t>
-  </si>
-  <si>
-    <t>0.9873,0.0009,0.0047,0.0005</t>
-  </si>
-  <si>
-    <t>0.9011,0.0131,0.0554,0.0031</t>
-  </si>
-  <si>
-    <t>0.9711,0.0051,0.0100,0.0018</t>
-  </si>
-  <si>
-    <t>0.8830,0.0131,0.0066,0.0504</t>
-  </si>
-  <si>
-    <t>0.9633,0.0014,0.0010,0.0295</t>
-  </si>
-  <si>
-    <t>0.9187,0.0084,0.0099,0.0250</t>
-  </si>
-  <si>
-    <t>0.9657,0.0024,0.0035,0.0205</t>
-  </si>
-  <si>
-    <t>0.9831,0.0015,0.0010,0.0058</t>
-  </si>
-  <si>
-    <t>0.9246,0.0083,0.0053,0.0312</t>
-  </si>
-  <si>
-    <t>0.9502,0.0005,0.0006,0.0645</t>
-  </si>
-  <si>
-    <t>0.9670,0.0013,0.0015,0.0181</t>
-  </si>
-  <si>
-    <t>0.9849,0.0016,0.0044,0.0006</t>
-  </si>
-  <si>
-    <t>0.9657,0.0074,0.0037,0.0027</t>
-  </si>
-  <si>
-    <t>0.9539,0.0066,0.0068,0.0042</t>
-  </si>
-  <si>
-    <t>0.9703,0.0043,0.0047,0.0059</t>
-  </si>
-  <si>
-    <t>0.9782,0.0007,0.0008,0.0133</t>
-  </si>
-  <si>
-    <t>0.9907,0.0006,0.0006,0.0020</t>
-  </si>
-  <si>
-    <t>0.9653,0.0020,0.0129,0.0025</t>
-  </si>
-  <si>
-    <t>0.9615,0.0022,0.0009,0.0188</t>
-  </si>
-  <si>
-    <t>0.0117,0.2659,0.9836,0.0010</t>
-  </si>
-  <si>
-    <t>0.9924,0.0006,0.0006,0.0011</t>
-  </si>
-  <si>
-    <t>0.2314,0.0088,0.9247,0.0004</t>
-  </si>
-  <si>
-    <t>0.9113,0.0025,0.1926,0.0001</t>
-  </si>
-  <si>
-    <t>0.9396,0.0007,0.1124,0.0003</t>
-  </si>
-  <si>
-    <t>0.5665,0.0118,0.7004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9157,0.0006,0.2400,0.0001</t>
-  </si>
-  <si>
-    <t>0.0313,0.0084,0.9871,0.0001</t>
-  </si>
-  <si>
-    <t>0.1028,0.0041,0.9355,0.0009</t>
-  </si>
-  <si>
-    <t>0.9603,0.0010,0.0406,0.0008</t>
-  </si>
-  <si>
-    <t>0.8616,0.0129,0.1640,0.0031</t>
-  </si>
-  <si>
-    <t>0.9829,0.0003,0.0155,0.0004</t>
-  </si>
-  <si>
-    <t>0.9342,0.0095,0.0634,0.0010</t>
-  </si>
-  <si>
-    <t>0.9379,0.0059,0.0446,0.0017</t>
-  </si>
-  <si>
-    <t>0.9549,0.0018,0.0493,0.0007</t>
-  </si>
-  <si>
-    <t>0.8542,0.0049,0.1451,0.0033</t>
-  </si>
-  <si>
-    <t>0.9617,0.0013,0.0293,0.0011</t>
-  </si>
-  <si>
-    <t>0.9693,0.0054,0.0112,0.0020</t>
-  </si>
-  <si>
-    <t>0.9867,0.0063,0.0007,0.0007</t>
-  </si>
-  <si>
-    <t>0.9744,0.0093,0.0017,0.0032</t>
-  </si>
-  <si>
-    <t>0.9648,0.0039,0.0016,0.0114</t>
-  </si>
-  <si>
-    <t>0.9633,0.0054,0.0040,0.0051</t>
-  </si>
-  <si>
-    <t>0.9853,0.0002,0.0098,0.0002</t>
-  </si>
-  <si>
-    <t>0.9524,0.0022,0.0588,0.0009</t>
-  </si>
-  <si>
-    <t>0.9901,0.0002,0.0074,0.0001</t>
-  </si>
-  <si>
-    <t>0.8807,0.0082,0.1337,0.0040</t>
-  </si>
-  <si>
-    <t>0.9591,0.0008,0.0334,0.0011</t>
-  </si>
-  <si>
-    <t>0.9921,0.0003,0.0078,0.0001</t>
-  </si>
-  <si>
-    <t>0.9911,0.0004,0.0060,0.0001</t>
-  </si>
-  <si>
-    <t>0.6285,0.0096,0.5775,0.0004</t>
-  </si>
-  <si>
-    <t>0.9285,0.0005,0.1382,0.0001</t>
-  </si>
-  <si>
-    <t>0.3136,0.0045,0.8619,0.0003</t>
-  </si>
-  <si>
-    <t>0.8644,0.0070,0.0043,0.0872</t>
-  </si>
-  <si>
-    <t>0.9495,0.0047,0.0062,0.0189</t>
-  </si>
-  <si>
-    <t>0.9455,0.0051,0.0032,0.0199</t>
-  </si>
-  <si>
-    <t>0.9384,0.0187,0.0102,0.0041</t>
-  </si>
-  <si>
-    <t>0.9410,0.0056,0.0066,0.0190</t>
-  </si>
-  <si>
-    <t>0.9896,0.0012,0.0009,0.0016</t>
-  </si>
-  <si>
-    <t>0.9230,0.0010,0.0014,0.0779</t>
-  </si>
-  <si>
-    <t>0.9737,0.0004,0.0002,0.0225</t>
-  </si>
-  <si>
-    <t>0.7467,0.0174,0.3932,0.0056</t>
-  </si>
-  <si>
-    <t>0.9113,0.0071,0.0422,0.0079</t>
-  </si>
-  <si>
-    <t>0.9884,0.0001,0.0018,0.0019</t>
-  </si>
-  <si>
-    <t>0.3143,0.0074,0.8695,0.0004</t>
-  </si>
-  <si>
-    <t>0.0174,0.0041,0.9816,0.0006</t>
-  </si>
-  <si>
-    <t>0.7752,0.0040,0.4505,0.0006</t>
-  </si>
-  <si>
-    <t>0.1098,0.0032,0.9653,0.0001</t>
-  </si>
-  <si>
-    <t>0.9886,0.0003,0.0150,0.0001</t>
-  </si>
-  <si>
-    <t>0.0051,0.0051,0.9972,0.0001</t>
-  </si>
-  <si>
-    <t>0.7479,0.0008,0.4758,0.0003</t>
-  </si>
-  <si>
-    <t>0.7893,0.0113,0.1381,0.0140</t>
-  </si>
-  <si>
-    <t>0.9502,0.0006,0.0613,0.0006</t>
-  </si>
-  <si>
-    <t>0.9936,0.0004,0.0029,0.0001</t>
-  </si>
-  <si>
-    <t>0.9879,0.0002,0.0068,0.0004</t>
-  </si>
-  <si>
-    <t>0.9545,0.0022,0.0046,0.0252</t>
-  </si>
-  <si>
-    <t>0.9622,0.0022,0.0050,0.0139</t>
-  </si>
-  <si>
-    <t>0.9864,0.0003,0.0003,0.0067</t>
-  </si>
-  <si>
-    <t>0.9611,0.0009,0.0032,0.0168</t>
-  </si>
-  <si>
-    <t>0.9882,0.0004,0.0002,0.0057</t>
-  </si>
-  <si>
-    <t>0.9693,0.0009,0.0014,0.0220</t>
-  </si>
-  <si>
-    <t>0.9638,0.0026,0.0030,0.0116</t>
-  </si>
-  <si>
-    <t>0.9570,0.0017,0.0008,0.0261</t>
-  </si>
-  <si>
-    <t>0.9799,0.0020,0.0144,0.0001</t>
-  </si>
-  <si>
-    <t>0.8676,0.0127,0.1700,0.0008</t>
-  </si>
-  <si>
-    <t>0.0623,0.0030,0.9781,0.0001</t>
-  </si>
-  <si>
-    <t>0.9440,0.0017,0.0973,0.0006</t>
-  </si>
-  <si>
-    <t>0.2518,0.0209,0.8947,0.0003</t>
-  </si>
-  <si>
-    <t>0.9816,0.0010,0.0050,0.0023</t>
-  </si>
-  <si>
-    <t>0.9867,0.0004,0.0129,0.0001</t>
-  </si>
-  <si>
-    <t>0.6697,0.0061,0.4966,0.0017</t>
-  </si>
-  <si>
-    <t>0.9918,0.0003,0.0023,0.0008</t>
-  </si>
-  <si>
-    <t>0.9450,0.0009,0.0081,0.0128</t>
-  </si>
-  <si>
-    <t>0.9855,0.0000,0.0006,0.0041</t>
-  </si>
-  <si>
-    <t>0.4552,0.0000,0.0013,0.6774</t>
-  </si>
-  <si>
-    <t>0.8098,0.0001,0.0021,0.1537</t>
-  </si>
-  <si>
-    <t>0.9758,0.0011,0.0192,0.0003</t>
+    <t>0.9282,0.0039,0.0240,0.0170</t>
+  </si>
+  <si>
+    <t>0.0108,0.0051,0.0006,0.9949</t>
+  </si>
+  <si>
+    <t>0.8903,0.0034,0.0023,0.1465</t>
+  </si>
+  <si>
+    <t>0.4008,0.0087,0.0004,0.6620</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9934,0.0020,0.0006,0.0020</t>
+  </si>
+  <si>
+    <t>0.9979,0.0003,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9985,0.0009,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0005,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9982,0.0004,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9982,0.0003,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9230,0.0027,0.1666,0.0006</t>
+  </si>
+  <si>
+    <t>0.0251,0.0046,0.9810,0.0012</t>
+  </si>
+  <si>
+    <t>0.6962,0.0175,0.3205,0.0002</t>
+  </si>
+  <si>
+    <t>0.1682,0.0068,0.8860,0.0014</t>
+  </si>
+  <si>
+    <t>0.7518,0.0035,0.3895,0.0035</t>
+  </si>
+  <si>
+    <t>0.0004,0.9984,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.9972,0.0022,0.0013</t>
+  </si>
+  <si>
+    <t>0.2099,0.8835,0.0065,0.0006</t>
+  </si>
+  <si>
+    <t>0.0025,0.9844,0.0055,0.0110</t>
+  </si>
+  <si>
+    <t>0.0032,0.9955,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.7145,0.0096,0.1681,0.0324</t>
+  </si>
+  <si>
+    <t>0.7878,0.0177,0.2751,0.0050</t>
+  </si>
+  <si>
+    <t>0.0095,0.0010,0.9927,0.0003</t>
+  </si>
+  <si>
+    <t>0.0592,0.0033,0.9485,0.0008</t>
+  </si>
+  <si>
+    <t>0.0154,0.0008,0.9914,0.0007</t>
+  </si>
+  <si>
+    <t>0.0024,0.0005,0.9972,0.0007</t>
+  </si>
+  <si>
+    <t>0.0033,0.0007,0.9966,0.0006</t>
+  </si>
+  <si>
+    <t>0.4587,0.4908,0.0705,0.0066</t>
+  </si>
+  <si>
+    <t>0.3920,0.2397,0.4210,0.0053</t>
+  </si>
+  <si>
+    <t>0.0023,0.0061,0.9952,0.0021</t>
+  </si>
+  <si>
+    <t>0.0204,0.8906,0.0659,0.0008</t>
+  </si>
+  <si>
+    <t>0.2654,0.6680,0.2048,0.0179</t>
+  </si>
+  <si>
+    <t>0.2761,0.0478,0.7158,0.0706</t>
+  </si>
+  <si>
+    <t>0.5536,0.6043,0.0018,0.0013</t>
+  </si>
+  <si>
+    <t>0.0550,0.9427,0.0857,0.0096</t>
+  </si>
+  <si>
+    <t>0.0126,0.8271,0.0789,0.0260</t>
+  </si>
+  <si>
+    <t>0.2882,0.0172,0.7999,0.0035</t>
+  </si>
+  <si>
+    <t>0.4780,0.0122,0.6498,0.0016</t>
+  </si>
+  <si>
+    <t>0.0022,0.0014,0.9915,0.0067</t>
+  </si>
+  <si>
+    <t>0.0055,0.0774,0.9912,0.0004</t>
+  </si>
+  <si>
+    <t>0.0064,0.9804,0.0100,0.0003</t>
+  </si>
+  <si>
+    <t>0.0055,0.0012,0.9943,0.0002</t>
+  </si>
+  <si>
+    <t>0.0125,0.1318,0.0099,0.9569</t>
+  </si>
+  <si>
+    <t>0.0051,0.9699,0.0144,0.0432</t>
+  </si>
+  <si>
+    <t>0.0131,0.9785,0.0180,0.0022</t>
+  </si>
+  <si>
+    <t>0.0001,0.9993,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.0055,0.0135,0.9782,0.0053</t>
+  </si>
+  <si>
+    <t>0.0029,0.3292,0.9894,0.0007</t>
+  </si>
+  <si>
+    <t>0.0450,0.0095,0.9467,0.0101</t>
+  </si>
+  <si>
+    <t>0.1447,0.0006,0.9226,0.0010</t>
+  </si>
+  <si>
+    <t>0.0044,0.0069,0.9898,0.0010</t>
+  </si>
+  <si>
+    <t>0.0010,0.1548,0.9883,0.0005</t>
+  </si>
+  <si>
+    <t>0.9936,0.0043,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.9788,0.0048,0.0186,0.0007</t>
+  </si>
+  <si>
+    <t>0.9954,0.0005,0.0003,0.0024</t>
+  </si>
+  <si>
+    <t>0.0061,0.0430,0.9873,0.0108</t>
+  </si>
+  <si>
+    <t>0.9910,0.0029,0.0041,0.0007</t>
+  </si>
+  <si>
+    <t>0.9946,0.0023,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.9903,0.0084,0.0016,0.0004</t>
+  </si>
+  <si>
+    <t>0.0077,0.8954,0.8645,0.0046</t>
+  </si>
+  <si>
+    <t>0.0024,0.0200,0.9923,0.0022</t>
+  </si>
+  <si>
+    <t>0.0023,0.0025,0.9964,0.0006</t>
+  </si>
+  <si>
+    <t>0.0029,0.8819,0.9434,0.0020</t>
+  </si>
+  <si>
+    <t>0.0003,0.0022,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.0182,0.9809,0.0051,0.0003</t>
+  </si>
+  <si>
+    <t>0.0055,0.9950,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8944,0.0095,0.1794,0.0028</t>
+  </si>
+  <si>
+    <t>0.7836,0.0073,0.4288,0.0011</t>
+  </si>
+  <si>
+    <t>0.0064,0.0028,0.9916,0.0012</t>
+  </si>
+  <si>
+    <t>0.0003,0.9819,0.9660,0.0002</t>
+  </si>
+  <si>
+    <t>0.0028,0.9797,0.6675,0.0011</t>
+  </si>
+  <si>
+    <t>0.0021,0.9926,0.0248,0.0004</t>
+  </si>
+  <si>
+    <t>0.0036,0.9673,0.5032,0.0024</t>
+  </si>
+  <si>
+    <t>0.0224,0.0013,0.0064,0.9854</t>
+  </si>
+  <si>
+    <t>0.0004,0.0015,0.0003,0.9994</t>
+  </si>
+  <si>
+    <t>0.0033,0.0011,0.0002,0.9986</t>
+  </si>
+  <si>
+    <t>0.0100,0.0004,0.0001,0.9974</t>
+  </si>
+  <si>
+    <t>0.0090,0.0008,0.0009,0.9971</t>
+  </si>
+  <si>
+    <t>0.0263,0.0101,0.0102,0.9814</t>
+  </si>
+  <si>
+    <t>0.0001,0.9924,0.9892,0.0001</t>
+  </si>
+  <si>
+    <t>0.0036,0.7549,0.9706,0.0018</t>
+  </si>
+  <si>
+    <t>0.0055,0.6281,0.6998,0.0010</t>
+  </si>
+  <si>
+    <t>0.0020,0.7403,0.9673,0.0007</t>
+  </si>
+  <si>
+    <t>0.0020,0.9931,0.1768,0.0004</t>
+  </si>
+  <si>
+    <t>0.0014,0.9428,0.7031,0.0005</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9964,0.0021,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9957,0.0027,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9970,0.0004,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.9982,0.0007,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9948,0.0022,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.9926,0.0041,0.0011,0.0013</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0007,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9971,0.0005,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9989,0.0003,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9983,0.0002,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.1402,0.0005,0.9563,0.0003</t>
+  </si>
+  <si>
+    <t>0.0062,0.0014,0.9934,0.0002</t>
+  </si>
+  <si>
+    <t>0.9543,0.0015,0.0087,0.0114</t>
+  </si>
+  <si>
+    <t>0.0040,0.0004,0.9953,0.0007</t>
+  </si>
+  <si>
+    <t>0.0066,0.9880,0.0024,0.0026</t>
+  </si>
+  <si>
+    <t>0.0010,0.9976,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.0802,0.9086,0.0146,0.0056</t>
+  </si>
+  <si>
+    <t>0.0442,0.9631,0.0023,0.0011</t>
+  </si>
+  <si>
+    <t>0.0057,0.9881,0.0013,0.0022</t>
+  </si>
+  <si>
+    <t>0.0058,0.9905,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.8679,0.1746,0.0058,0.0018</t>
+  </si>
+  <si>
+    <t>0.7542,0.0112,0.3560,0.0091</t>
+  </si>
+  <si>
+    <t>0.0451,0.0055,0.9629,0.0022</t>
+  </si>
+  <si>
+    <t>0.7909,0.0962,0.0761,0.0311</t>
+  </si>
+  <si>
+    <t>0.7722,0.1052,0.1234,0.0174</t>
+  </si>
+  <si>
+    <t>0.0402,0.0354,0.0408,0.9471</t>
+  </si>
+  <si>
+    <t>0.0024,0.9942,0.0218,0.0018</t>
+  </si>
+  <si>
+    <t>0.0017,0.9879,0.0089,0.0119</t>
+  </si>
+  <si>
+    <t>0.0049,0.9809,0.0095,0.0045</t>
+  </si>
+  <si>
+    <t>0.0014,0.9611,0.9233,0.0018</t>
+  </si>
+  <si>
+    <t>0.0024,0.9919,0.0111,0.0064</t>
+  </si>
+  <si>
+    <t>0.8945,0.1126,0.0122,0.0057</t>
+  </si>
+  <si>
+    <t>0.6259,0.5132,0.0078,0.0015</t>
+  </si>
+  <si>
+    <t>0.9956,0.0017,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9944,0.0004,0.0002,0.0037</t>
+  </si>
+  <si>
+    <t>0.9932,0.0008,0.0058,0.0003</t>
+  </si>
+  <si>
+    <t>0.9953,0.0011,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.9990,0.0000,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9824,0.0145,0.0031,0.0010</t>
+  </si>
+  <si>
+    <t>0.9898,0.0040,0.0017,0.0022</t>
+  </si>
+  <si>
+    <t>0.9965,0.0004,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.0002,0.9694,0.9937,0.0001</t>
+  </si>
+  <si>
+    <t>0.0079,0.5394,0.9586,0.0005</t>
+  </si>
+  <si>
+    <t>0.0427,0.0912,0.9300,0.0022</t>
+  </si>
+  <si>
+    <t>0.4296,0.0031,0.7519,0.0008</t>
+  </si>
+  <si>
+    <t>0.9953,0.0006,0.0022,0.0001</t>
+  </si>
+  <si>
+    <t>0.6049,0.0124,0.3694,0.0235</t>
+  </si>
+  <si>
+    <t>0.3380,0.0007,0.8390,0.0012</t>
+  </si>
+  <si>
+    <t>0.8440,0.0114,0.1565,0.0098</t>
+  </si>
+  <si>
+    <t>0.1521,0.0041,0.0016,0.9433</t>
+  </si>
+  <si>
+    <t>0.0005,0.0008,0.0013,0.9993</t>
+  </si>
+  <si>
+    <t>0.0006,0.0068,0.0000,0.9993</t>
+  </si>
+  <si>
+    <t>0.0149,0.0004,0.0018,0.9940</t>
+  </si>
+  <si>
+    <t>0.0006,0.9946,0.0831,0.0004</t>
+  </si>
+  <si>
+    <t>0.9956,0.0011,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.1760,0.8062,0.0294,0.0233</t>
+  </si>
+  <si>
+    <t>0.9973,0.0006,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.4259,0.6491,0.0120,0.0012</t>
+  </si>
+  <si>
+    <t>0.9952,0.0003,0.0005,0.0022</t>
+  </si>
+  <si>
+    <t>0.9186,0.0024,0.0010,0.1252</t>
+  </si>
+  <si>
+    <t>0.9946,0.0004,0.0011,0.0013</t>
+  </si>
+  <si>
+    <t>0.0186,0.2175,0.9289,0.0869</t>
+  </si>
+  <si>
+    <t>0.8350,0.0007,0.0013,0.2676</t>
+  </si>
+  <si>
+    <t>0.8989,0.0039,0.0012,0.1215</t>
+  </si>
+  <si>
+    <t>0.2191,0.7728,0.0463,0.0080</t>
+  </si>
+  <si>
+    <t>0.9910,0.0007,0.0023,0.0013</t>
+  </si>
+  <si>
+    <t>0.9658,0.0129,0.0113,0.0045</t>
+  </si>
+  <si>
+    <t>0.2739,0.5544,0.0882,0.0839</t>
+  </si>
+  <si>
+    <t>0.8605,0.1007,0.0305,0.0172</t>
+  </si>
+  <si>
+    <t>0.9841,0.0066,0.0044,0.0006</t>
+  </si>
+  <si>
+    <t>0.9949,0.0007,0.0008,0.0011</t>
+  </si>
+  <si>
+    <t>0.9975,0.0005,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9936,0.0008,0.0009,0.0022</t>
+  </si>
+  <si>
+    <t>0.9978,0.0001,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9900,0.0016,0.0027,0.0034</t>
+  </si>
+  <si>
+    <t>0.9807,0.0109,0.0057,0.0021</t>
+  </si>
+  <si>
+    <t>0.9929,0.0011,0.0011,0.0018</t>
+  </si>
+  <si>
+    <t>0.9966,0.0003,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.8957,0.0539,0.0022,0.0190</t>
+  </si>
+  <si>
+    <t>0.6182,0.5249,0.0046,0.0018</t>
+  </si>
+  <si>
+    <t>0.9614,0.0427,0.0048,0.0019</t>
+  </si>
+  <si>
+    <t>0.9705,0.0086,0.0060,0.0076</t>
+  </si>
+  <si>
+    <t>0.9922,0.0137,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.8937,0.1318,0.0064,0.0027</t>
+  </si>
+  <si>
+    <t>0.9809,0.0084,0.0080,0.0007</t>
+  </si>
+  <si>
+    <t>0.9184,0.1357,0.0015,0.0012</t>
+  </si>
+  <si>
+    <t>0.0009,0.0148,0.9982,0.0019</t>
+  </si>
+  <si>
+    <t>0.9904,0.0032,0.0027,0.0007</t>
+  </si>
+  <si>
+    <t>0.0013,0.0048,0.9957,0.0003</t>
+  </si>
+  <si>
+    <t>0.0069,0.0252,0.9904,0.0014</t>
+  </si>
+  <si>
+    <t>0.1968,0.0027,0.9077,0.0014</t>
+  </si>
+  <si>
+    <t>0.0097,0.0334,0.9799,0.0029</t>
+  </si>
+  <si>
+    <t>0.0031,0.0052,0.9952,0.0007</t>
+  </si>
+  <si>
+    <t>0.0042,0.0010,0.9946,0.0006</t>
+  </si>
+  <si>
+    <t>0.0008,0.0002,0.9986,0.0003</t>
+  </si>
+  <si>
+    <t>0.0235,0.0262,0.9059,0.0599</t>
+  </si>
+  <si>
+    <t>0.2775,0.0083,0.8180,0.0028</t>
+  </si>
+  <si>
+    <t>0.1282,0.0060,0.9388,0.0028</t>
+  </si>
+  <si>
+    <t>0.0772,0.0770,0.8675,0.0036</t>
+  </si>
+  <si>
+    <t>0.2224,0.4114,0.4520,0.0121</t>
+  </si>
+  <si>
+    <t>0.2677,0.0386,0.7488,0.0061</t>
+  </si>
+  <si>
+    <t>0.5521,0.0039,0.5755,0.0065</t>
+  </si>
+  <si>
+    <t>0.1497,0.2454,0.5348,0.0183</t>
+  </si>
+  <si>
+    <t>0.7374,0.3791,0.0075,0.0004</t>
+  </si>
+  <si>
+    <t>0.9255,0.1387,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9845,0.0163,0.0006,0.0014</t>
+  </si>
+  <si>
+    <t>0.9911,0.0132,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9904,0.0118,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9650,0.0062,0.0229,0.0015</t>
+  </si>
+  <si>
+    <t>0.9704,0.0019,0.0195,0.0017</t>
+  </si>
+  <si>
+    <t>0.8074,0.0013,0.1098,0.0190</t>
+  </si>
+  <si>
+    <t>0.7017,0.0004,0.4935,0.0006</t>
+  </si>
+  <si>
+    <t>0.8019,0.0039,0.2683,0.0056</t>
+  </si>
+  <si>
+    <t>0.0084,0.0043,0.9884,0.0065</t>
+  </si>
+  <si>
+    <t>0.0071,0.0260,0.9761,0.0049</t>
+  </si>
+  <si>
+    <t>0.0055,0.0034,0.9946,0.0007</t>
+  </si>
+  <si>
+    <t>0.0715,0.0781,0.8930,0.0053</t>
+  </si>
+  <si>
+    <t>0.0042,0.0074,0.9756,0.0086</t>
+  </si>
+  <si>
+    <t>0.9952,0.0005,0.0001,0.0027</t>
+  </si>
+  <si>
+    <t>0.9932,0.0014,0.0005,0.0027</t>
+  </si>
+  <si>
+    <t>0.9915,0.0072,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.9966,0.0015,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9957,0.0011,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.9980,0.0003,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9965,0.0016,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9975,0.0004,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.0070,0.2867,0.9805,0.0056</t>
+  </si>
+  <si>
+    <t>0.0318,0.0343,0.9364,0.0215</t>
+  </si>
+  <si>
+    <t>0.5782,0.0445,0.3157,0.0326</t>
+  </si>
+  <si>
+    <t>0.0237,0.0041,0.9830,0.0009</t>
+  </si>
+  <si>
+    <t>0.0017,0.0014,0.9933,0.0013</t>
+  </si>
+  <si>
+    <t>0.0029,0.0826,0.9878,0.0009</t>
+  </si>
+  <si>
+    <t>0.0073,0.0007,0.9964,0.0001</t>
+  </si>
+  <si>
+    <t>0.0532,0.0091,0.9309,0.0030</t>
+  </si>
+  <si>
+    <t>0.0024,0.0023,0.9955,0.0008</t>
+  </si>
+  <si>
+    <t>0.0008,0.0028,0.9975,0.0006</t>
+  </si>
+  <si>
+    <t>0.0707,0.0199,0.8980,0.0084</t>
+  </si>
+  <si>
+    <t>0.9020,0.0006,0.1844,0.0007</t>
+  </si>
+  <si>
+    <t>0.0916,0.0014,0.9497,0.0009</t>
+  </si>
+  <si>
+    <t>0.9875,0.0002,0.0070,0.0008</t>
+  </si>
+  <si>
+    <t>0.9954,0.0047,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9981,0.0003,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9975,0.0014,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9885,0.0092,0.0028,0.0008</t>
+  </si>
+  <si>
+    <t>0.9979,0.0004,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9980,0.0008,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9986,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0118,0.0061,0.9832,0.0008</t>
+  </si>
+  <si>
+    <t>0.0049,0.0182,0.9870,0.0054</t>
+  </si>
+  <si>
+    <t>0.0068,0.0064,0.9884,0.0014</t>
+  </si>
+  <si>
+    <t>0.0222,0.0246,0.9418,0.0232</t>
+  </si>
+  <si>
+    <t>0.0160,0.0010,0.9890,0.0004</t>
+  </si>
+  <si>
+    <t>0.7643,0.0010,0.0386,0.0799</t>
+  </si>
+  <si>
+    <t>0.7552,0.0028,0.3632,0.0017</t>
+  </si>
+  <si>
+    <t>0.0805,0.0022,0.8025,0.0194</t>
+  </si>
+  <si>
+    <t>0.4441,0.0024,0.0074,0.6479</t>
+  </si>
+  <si>
+    <t>0.0029,0.0305,0.0009,0.9958</t>
+  </si>
+  <si>
+    <t>0.0173,0.0009,0.0021,0.9910</t>
+  </si>
+  <si>
+    <t>0.0025,0.0001,0.0001,0.9994</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.0001,0.9998</t>
+  </si>
+  <si>
+    <t>0.9050,0.0008,0.0006,0.1291</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2233,7 +2233,7 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
         <v>284</v>
@@ -2247,7 +2247,7 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s">
         <v>285</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2415,7 +2415,7 @@
         <v>259</v>
       </c>
       <c r="C35" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D35" t="s">
         <v>297</v>
@@ -2429,7 +2429,7 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
         <v>298</v>
@@ -2443,7 +2443,7 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
         <v>299</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3451,7 +3451,7 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D109" t="s">
         <v>371</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3521,7 +3521,7 @@
         <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D114" t="s">
         <v>376</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3703,7 +3703,7 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
         <v>389</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4151,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
         <v>421</v>
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4361,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
         <v>436</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4655,7 +4655,7 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
         <v>457</v>
@@ -4669,7 +4669,7 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
         <v>458</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5187,7 +5187,7 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
         <v>495</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5439,7 +5439,7 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
         <v>513</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
